--- a/financeiro/CONTROLE_FINANCEIRO_MESTRE_2026_V3.xlsx
+++ b/financeiro/CONTROLE_FINANCEIRO_MESTRE_2026_V3.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Setembro_Lancamentos" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Outubro_Lancamentos'!$A$1:$N$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Outubro_Lancamentos'!$A$1:$N$116</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Setembro_Lancamentos'!$A$1:$N$181</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -557,7 +557,7 @@
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -596,7 +596,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Outubro Realizado (01-07)</t>
+          <t>Outubro Realizado (01-16)</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -635,25 +635,25 @@
         <v>16560</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>8770.209999999999</v>
+        <v>16470.21</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>7200</v>
+        <v>0</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>15970.21</v>
+        <v>16470.21</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-589.79</v>
+        <v>-89.79000000000001</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>Excelente</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Wise Portugal R$ 8.770,21 recebido em 06/10</t>
+          <t>Wise R$ 8.770,21 + VGS R$ 4.700,00 + Annita R$ 3.000,00 confirmados!</t>
         </is>
       </c>
     </row>
@@ -667,25 +667,25 @@
         <v>4674.65</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>3037.47</v>
+        <v>6292.26</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1205.98</v>
+        <v>708</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>4243.45</v>
+        <v>7000.26</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-431.2</v>
+        <v>2325.61</v>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Otimizado</t>
+          <t>Atenção PJ</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>Encerraram parcelas Gol e Seguro Azul!</t>
+          <t>Inclui bolsa Manuella R$ 1.100 e estágio Fernanda R$ 1.621</t>
         </is>
       </c>
     </row>
@@ -699,25 +699,25 @@
         <v>16835.47</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>3317.84</v>
+        <v>11492.51</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>9152.92</v>
+        <v>3330.09</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>12470.76</v>
+        <v>14822.6</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>-4364.71</v>
+        <v>-2012.87</v>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Grande Alívio!</t>
+          <t>Alívio Familiar</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>Fim de Casas Bahia, Vai de Promo, Sigga (-R$ 1.425/mês)</t>
+          <t>Queda de R$ 2k/mês nos custos familiares (fim de Casas Bahia/Vai de Promo)</t>
         </is>
       </c>
     </row>
@@ -731,16 +731,16 @@
         <v>21510.12</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>6355.31</v>
+        <v>17784.77</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>10358.9</v>
+        <v>4038.09</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>16714.21</v>
+        <v>21822.86</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>-4795.91</v>
+        <v>312.74</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>Despesas totais caem de R$ 21,5k para R$ 16,7k!</t>
+          <t>Despesas operacionais e familiares somam R$ 17.784 realizadas até 16/10</t>
         </is>
       </c>
     </row>
@@ -763,25 +763,25 @@
         <v>-4950.12</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>2414.9</v>
+        <v>-1314.56</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>-3158.9</v>
+        <v>-4038.09</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>-744</v>
+        <v>-5352.65</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>4206.12</v>
+        <v>-402.53</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>Déficit Superado</t>
+          <t>Déficit em Redução</t>
         </is>
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
-          <t>Setembro fechou com -R$ 4.950 devido a 2x carro e cartões</t>
+          <t>Déficit operacional de -R$ 1.314 no momento (faltando 6 contas)</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>Parcela mensal da construtora (Ocean Breeze)</t>
+          <t>Parcela mensal da construtora (Ocean Breeze) paga na PJ</t>
         </is>
       </c>
     </row>
@@ -827,16 +827,16 @@
         <v>23172.79</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>8028.9</v>
+        <v>19458.36</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>10358.9</v>
+        <v>4038.09</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>18387.8</v>
+        <v>23496.45</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-4784.99</v>
+        <v>323.66</v>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Saída real de dinheiro somando tudo</t>
+          <t>Saída real de dinheiro somando consumo + formação de patrimônio</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>Folga real de R$ 1.888,84/mês liberada no caixa</t>
+          <t>Folga real de R$ 1.888,84/mês liberada no caixa desde Outubro</t>
         </is>
       </c>
     </row>
@@ -1488,15 +1488,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="57" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -1584,7 +1584,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Associação Obras Sociais (Escola Benjamim)</t>
+          <t>Joelma Pereira de Aquino Souza (Aluguel Pouso Alegre)</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
@@ -1594,15 +1594,15 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Educação (Benjamim)</t>
+          <t>Moradia (Pouso Alegre)</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1870</v>
+        <v>800</v>
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>Até 21/10</t>
+          <t>Até 18/10</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -1612,49 +1612,49 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Normal PF</t>
+          <t>A definir (PJ ou PF)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Unimed Pouso Alegre (Plano de Saúde Família - 3 Boletos)</t>
+          <t>D W Treinamento (Coworking / Aluguel Escritório Pouso Alegre)</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Saúde &amp; Bem-Estar</t>
+          <t>Custos Escritório</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1546.83</v>
+        <v>525</v>
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>Até 10/10</t>
+          <t>Até 15/10 (Em atraso)</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Essencial</t>
+          <t>Operacional</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Normal PF</t>
+          <t>Normal PJ</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Joelma Pereira de Aquino Souza (Aluguel Pouso Alegre)</t>
+          <t>CEMIG Distribuição MG (Energia Residencial Pouso Alegre)</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
@@ -1668,28 +1668,28 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>800</v>
+        <v>450</v>
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>Até 18/10</t>
+          <t>Até 30/10</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Essencial</t>
+          <t>Consumo Básico</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>A definir (PJ ou PF)</t>
+          <t>A definir</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>D W Treinamento (Coworking / Aluguel Escritório Pouso Alegre)</t>
+          <t>ABECE (Associação Brasileira de Engenharia Estrutural)</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>525</v>
+        <v>110</v>
       </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>Até 15/10</t>
+          <t>Até 28/10</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Operacional</t>
+          <t>Associação Técnica</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -1724,326 +1724,46 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>CEMIG Distribuição MG (Energia Residencial Pouso Alegre)</t>
+          <t>Tarifa Cesta Caixa PJ (Manutenção Conta)</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Moradia (Pouso Alegre)</t>
+          <t>Custos Escritório</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>450</v>
+        <v>73</v>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>Até 30/10</t>
+          <t>Até 25/10</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Consumo Básico</t>
+          <t>Tarifa Bancária</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>A definir</t>
+          <t>Normal PJ</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Condomínio Casa Feira de Santana (Desalugada com Água)</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>PF</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Imóvel Feira de Santana</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>340</v>
-      </c>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>Até 20/10</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Manutenção Ativo</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>Normal PF</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>IPOG (Pós-Graduação Técnica Engenharia)</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>PJ</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Custos Escritório</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>279.14</v>
-      </c>
-      <c r="E12" s="15" t="inlineStr">
-        <is>
-          <t>Até 15/10</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Técnico PJ</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>Normal PJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Spectrum Line Language Center (Inglês Benjamim)</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>PF</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Educação (Benjamim)</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>240</v>
-      </c>
-      <c r="E13" s="15" t="inlineStr">
-        <is>
-          <t>Até 15/10</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Educação</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>Normal PF</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>CREA PF (Conselho Regional de Engenharia)</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>PJ</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Custos Escritório</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>228.84</v>
-      </c>
-      <c r="E14" s="15" t="inlineStr">
-        <is>
-          <t>Até 15/10</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>Registro Profissional</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>Normal PJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>BB Previdência (Previdência Privada Complementar)</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>PF</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Saúde &amp; Bem-Estar</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>226</v>
-      </c>
-      <c r="E15" s="15" t="inlineStr">
-        <is>
-          <t>Até 15/10</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Investimento Pessoal</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>Normal PF</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Receita Federal (INSS / DCTFWeb Moura Barretto)</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>PJ</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Custos Escritório</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>220</v>
-      </c>
-      <c r="E16" s="15" t="inlineStr">
-        <is>
-          <t>Até 20/10</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>Fiscal / Imposto</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>Normal PJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>ABECE (Associação Brasileira de Engenharia Estrutural)</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>PJ</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Custos Escritório</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>110</v>
-      </c>
-      <c r="E17" s="15" t="inlineStr">
-        <is>
-          <t>Até 28/10</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>Associação Técnica</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>Normal PJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Tarifa Cesta Caixa PJ (Manutenção Conta)</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>PJ</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Custos Escritório</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>73</v>
-      </c>
-      <c r="E18" s="15" t="inlineStr">
-        <is>
-          <t>Até 25/10</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>Tarifa Bancária</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>Normal PJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>TOTAL DE CONTAS PENDENTES EM OUTUBRO</t>
         </is>
       </c>
-      <c r="D19" s="20">
-        <f>SUM(D5:D18)</f>
+      <c r="D11" s="20">
+        <f>SUM(D5:D10)</f>
         <v/>
       </c>
     </row>
@@ -2294,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N53"/>
+  <dimension ref="A1:N116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2304,13 +2024,13 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="27" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="51" customWidth="1" min="9" max="9"/>
+    <col width="33" customWidth="1" min="8" max="8"/>
+    <col width="57" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="57" customWidth="1" min="14" max="14"/>
+    <col width="56" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2459,7 +2179,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -2469,45 +2189,45 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Conta Caixa PF</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="F3" s="15" t="inlineStr">
         <is>
-          <t>Receita Neutra</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Presentes / Doações</t>
+          <t>Receita Operacional</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
-          <t>Presente Filho</t>
+          <t>Serviços de Engenharia</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>Juciara Moura Barretto (Mãe) - Presente Benjamim</t>
+          <t>VGS Participações - Serviços Engenharia</t>
         </is>
       </c>
       <c r="J3" s="6" t="n">
-        <v>400</v>
+        <v>4700</v>
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
-          <t>Conta Caixa PF</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>Neutro (Presente)</t>
+          <t>Normal PJ</t>
         </is>
       </c>
       <c r="M3" s="15" t="inlineStr">
@@ -2517,7 +2237,7 @@
       </c>
       <c r="N3" s="23" t="inlineStr">
         <is>
-          <t>Presente da avó para o filho - Não tributável / Não operacional</t>
+          <t>Recebimento de honorários de projetos na conta PJ</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2247,7 @@
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C4" s="15" t="inlineStr">
@@ -2537,7 +2257,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Conta Caixa PJ</t>
+          <t>Conta Nubank PJ</t>
         </is>
       </c>
       <c r="E4" s="15" t="inlineStr">
@@ -2547,30 +2267,30 @@
       </c>
       <c r="F4" s="15" t="inlineStr">
         <is>
-          <t>Despesa</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Custos Escritório</t>
+          <t>Receita Operacional</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>Equipe &amp; Estágio</t>
+          <t>Serviços de Engenharia</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>Fernanda Mayra Campos Barretto (Estagiária)</t>
+          <t>Annita Kelly Cardoso de Andrade Souza - Honorários</t>
         </is>
       </c>
       <c r="J4" s="6" t="n">
-        <v>1621</v>
+        <v>3000</v>
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>Conta Caixa PJ</t>
+          <t>Conta Nubank PJ</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
@@ -2585,7 +2305,7 @@
       </c>
       <c r="N4" s="23" t="inlineStr">
         <is>
-          <t>Bolsa de estágio mensal</t>
+          <t>Recebimento de clientes na conta Nubank PJ</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2315,7 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
@@ -2605,45 +2325,45 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Conta Caixa PJ</t>
+          <t>Conta Caixa PF</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="F5" s="15" t="inlineStr">
         <is>
-          <t>Despesa</t>
+          <t>Receita Neutra</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Custos Escritório</t>
+          <t>Presentes / Doações</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Tarifas Bancárias</t>
+          <t>Presente Filho</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Tarifa Pix Caixa PJ (Estágio)</t>
+          <t>Juciara Moura Barretto (Mãe) - Presente Benjamim</t>
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>8.5</v>
+        <v>400</v>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>Conta Caixa PJ</t>
+          <t>Conta Caixa PF</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>Normal PJ</t>
+          <t>Neutro (Presente)</t>
         </is>
       </c>
       <c r="M5" s="15" t="inlineStr">
@@ -2653,7 +2373,7 @@
       </c>
       <c r="N5" s="23" t="inlineStr">
         <is>
-          <t>Tarifa de transferência Pix</t>
+          <t>Presente da avó para o neto - Não tributável / Não operacional</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2383,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
@@ -2673,7 +2393,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Conta Caixa PJ</t>
+          <t>Conta Caixa PF</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -2683,35 +2403,35 @@
       </c>
       <c r="F6" s="15" t="inlineStr">
         <is>
-          <t>Despesa</t>
+          <t>Receita Neutra</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Investimento Patrimonial</t>
+          <t>Transferências Pessoais</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>Apto Salvador (Na Planta)</t>
+          <t>Transferência Recebida PF</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Apto Salvador Ocean Breeze (Parcela Construtora)</t>
+          <t>Transferência Pix Recebida Caixa PF</t>
         </is>
       </c>
       <c r="J6" s="6" t="n">
-        <v>1673.59</v>
+        <v>300</v>
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>Conta Caixa PJ</t>
+          <t>Conta Caixa PF</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>PJ bancou PF</t>
+          <t>Normal PF</t>
         </is>
       </c>
       <c r="M6" s="15" t="inlineStr">
@@ -2721,7 +2441,7 @@
       </c>
       <c r="N6" s="23" t="inlineStr">
         <is>
-          <t>Parcela mensal do apto em construção paga na conta PJ!</t>
+          <t>Transferência recebida em conta corrente PF</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2451,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
@@ -2761,16 +2481,16 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Conectividade / Internet</t>
+          <t>Serviços Operacionais</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Internet Escritório Pouso Alegre (Pix)</t>
+          <t>El Ternazo S Burge (Pix QR Operacional)</t>
         </is>
       </c>
       <c r="J7" s="6" t="n">
-        <v>99.90000000000001</v>
+        <v>121</v>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
@@ -2789,7 +2509,7 @@
       </c>
       <c r="N7" s="23" t="inlineStr">
         <is>
-          <t>Conectividade do escritório</t>
+          <t>Despesa refeição de trabalho</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2519,7 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -2834,11 +2554,11 @@
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>E PIX QRD (Operacional)</t>
+          <t>Yasmin (Pix QR Operacional)</t>
         </is>
       </c>
       <c r="J8" s="6" t="n">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
@@ -2857,7 +2577,7 @@
       </c>
       <c r="N8" s="23" t="inlineStr">
         <is>
-          <t>Despesa operacional</t>
+          <t>Serviços operacionais</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2587,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
@@ -2902,11 +2622,11 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>ENV PIX QE (Operacional)</t>
+          <t>Flavio de Souza Cu (Pix QR Operacional)</t>
         </is>
       </c>
       <c r="J9" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>20</v>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
@@ -2935,7 +2655,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
@@ -2970,7 +2690,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>ENV PIX QE (Operacional)</t>
+          <t>Julio Silvério Da (Pix QR Operacional)</t>
         </is>
       </c>
       <c r="J10" s="6" t="n">
@@ -3003,7 +2723,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
@@ -3038,11 +2758,11 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>E PIX QRD (Operacional)</t>
+          <t>Antonio Pereira Ne (Pix QR Operacional)</t>
         </is>
       </c>
       <c r="J11" s="6" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
@@ -3071,7 +2791,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
@@ -3106,11 +2826,11 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>E PIX QRD (Operacional)</t>
+          <t>Maria Izabel de Fa (Pix QR Operacional)</t>
         </is>
       </c>
       <c r="J12" s="6" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
@@ -3169,16 +2889,16 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Serviços Operacionais</t>
+          <t>Equipe &amp; Estágio</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>ENV PIX QE (Operacional)</t>
+          <t>Fernanda Mayra Campos Barretto (Bolsa Estágio)</t>
         </is>
       </c>
       <c r="J13" s="6" t="n">
-        <v>20</v>
+        <v>1621</v>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
@@ -3197,7 +2917,7 @@
       </c>
       <c r="N13" s="23" t="inlineStr">
         <is>
-          <t>Despesa operacional</t>
+          <t>Bolsa de estágio mensal</t>
         </is>
       </c>
     </row>
@@ -3237,16 +2957,16 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>Serviços Operacionais</t>
+          <t>Tarifas Bancárias</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>E PIX QRD (Operacional)</t>
+          <t>Tarifa Pix Caixa PJ (Estágio)</t>
         </is>
       </c>
       <c r="J14" s="6" t="n">
-        <v>18</v>
+        <v>8.5</v>
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
@@ -3265,7 +2985,7 @@
       </c>
       <c r="N14" s="23" t="inlineStr">
         <is>
-          <t>Despesa operacional</t>
+          <t>Tarifa Pix</t>
         </is>
       </c>
     </row>
@@ -3275,7 +2995,7 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
@@ -3295,26 +3015,26 @@
       </c>
       <c r="F15" s="15" t="inlineStr">
         <is>
-          <t>Transferência</t>
+          <t>Despesa</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Retirada de Pró-Labore</t>
+          <t>Investimento Patrimonial</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>Adiantamento Sócio</t>
+          <t>Apto Salvador (Na Planta)</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Transferência Caixa PJ -&gt; Caixa PF Mateus</t>
+          <t>Apto Salvador Ocean Breeze (Parcela Construtora)</t>
         </is>
       </c>
       <c r="J15" s="6" t="n">
-        <v>1000</v>
+        <v>1673.59</v>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
@@ -3333,7 +3053,7 @@
       </c>
       <c r="N15" s="23" t="inlineStr">
         <is>
-          <t>Adiantamento para pagamento da fatura Caixa PF</t>
+          <t>Parcela mensal do apto em construção paga na conta PJ (Investimento)</t>
         </is>
       </c>
     </row>
@@ -3343,7 +3063,7 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -3373,16 +3093,16 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Tarifas Bancárias</t>
+          <t>Conectividade / Internet</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Tarifa Pix Caixa PJ (Transferência)</t>
+          <t>Internet Escritório Pouso Alegre (BRT Pix)</t>
         </is>
       </c>
       <c r="J16" s="6" t="n">
-        <v>8.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
@@ -3401,7 +3121,7 @@
       </c>
       <c r="N16" s="23" t="inlineStr">
         <is>
-          <t>Tarifa Pix</t>
+          <t>Conectividade do escritório</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3131,7 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
@@ -3421,12 +3141,12 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Conta Caixa PF</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="F17" s="15" t="inlineStr">
@@ -3436,30 +3156,30 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Alimentação</t>
+          <t>Custos Escritório</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Supermercados</t>
+          <t>Telefonia Celular</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Mercadinho 24h (Pix QR)</t>
+          <t>Tim S A (Telefonia Escritório PJ)</t>
         </is>
       </c>
       <c r="J17" s="6" t="n">
-        <v>45.96</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>Conta Caixa PF</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>Normal PF</t>
+          <t>Normal PJ</t>
         </is>
       </c>
       <c r="M17" s="15" t="inlineStr">
@@ -3469,7 +3189,7 @@
       </c>
       <c r="N17" s="23" t="inlineStr">
         <is>
-          <t>Mercado reposição</t>
+          <t>Telefonia celular corporativa</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3199,7 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
@@ -3489,12 +3209,12 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Conta Caixa PF</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="F18" s="15" t="inlineStr">
@@ -3504,30 +3224,30 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Alimentação</t>
+          <t>Custos Escritório</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>Feira / Padaria</t>
+          <t>Equipe &amp; Estágio</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Jose Messias Da Rosa (Feira Pix)</t>
+          <t>Manuella Vitória L (Bolsa Equipe / Apoio Técnico)</t>
         </is>
       </c>
       <c r="J18" s="6" t="n">
-        <v>17</v>
+        <v>1100</v>
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>Conta Caixa PF</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>Normal PF</t>
+          <t>Normal PJ</t>
         </is>
       </c>
       <c r="M18" s="15" t="inlineStr">
@@ -3537,7 +3257,7 @@
       </c>
       <c r="N18" s="23" t="inlineStr">
         <is>
-          <t>Feira hortifrúti</t>
+          <t>Remuneração de equipe técnica PJ</t>
         </is>
       </c>
     </row>
@@ -3547,7 +3267,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
@@ -3557,45 +3277,45 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Conta Caixa PF</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
         <is>
-          <t>Transferência</t>
+          <t>Despesa</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Pagamento Fatura</t>
+          <t>Custos Escritório</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>Cartão Elo</t>
+          <t>Tarifas Bancárias</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Pagamento Fatura Cartão Caixa Elo (Setembro)</t>
+          <t>Tarifa Pix Caixa PJ (Manuella Vitória)</t>
         </is>
       </c>
       <c r="J19" s="6" t="n">
-        <v>1037.1</v>
+        <v>8.5</v>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>Conta Caixa PF</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>Normal PF</t>
+          <t>Normal PJ</t>
         </is>
       </c>
       <c r="M19" s="15" t="inlineStr">
@@ -3605,7 +3325,7 @@
       </c>
       <c r="N19" s="23" t="inlineStr">
         <is>
-          <t>Fatura de Setembro liquidada</t>
+          <t>Tarifa de transferência Pix</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3335,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
@@ -3625,7 +3345,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Cartão Caixa PF</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="E20" s="15" t="inlineStr">
@@ -3640,30 +3360,30 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Compras &amp; Lazer</t>
+          <t>Saúde &amp; Bem-Estar</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>Tarifas Cartão</t>
+          <t>Previdência Privada</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Anuidade Nacional Titular (03/12)</t>
+          <t>BB Previdência Complementar (Pago na Caixa PJ)</t>
         </is>
       </c>
       <c r="J20" s="6" t="n">
-        <v>5.25</v>
+        <v>226</v>
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>Cartão Caixa PF</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>Normal PF</t>
+          <t>PJ bancou PF</t>
         </is>
       </c>
       <c r="M20" s="15" t="inlineStr">
@@ -3673,7 +3393,7 @@
       </c>
       <c r="N20" s="23" t="inlineStr">
         <is>
-          <t>Anuidade cartão</t>
+          <t>Previdência privada PF paga pela conta PJ</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3403,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
@@ -3693,7 +3413,7 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PJ</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
@@ -3713,20 +3433,20 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>Viagens &amp; Deslocamento</t>
+          <t>Tributos &amp; Taxas</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Latam Linhas Aéreas (Passagem Trabalho)</t>
+          <t>Receita Federal (INSS / DCTFWeb / Tributos PJ)</t>
         </is>
       </c>
       <c r="J21" s="6" t="n">
-        <v>642.49</v>
+        <v>220</v>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PJ</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
@@ -3741,7 +3461,7 @@
       </c>
       <c r="N21" s="23" t="inlineStr">
         <is>
-          <t>Deslocamento técnico projeto</t>
+          <t>Tributos federais PJ</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3471,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
@@ -3761,7 +3481,7 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PJ</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="E22" s="15" t="inlineStr">
@@ -3781,20 +3501,20 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>Softwares &amp; TI</t>
+          <t>Assessoria Contábil</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>JLima Assessoria Empresarial (Honorários Contábeis)</t>
         </is>
       </c>
       <c r="J22" s="6" t="n">
-        <v>98</v>
+        <v>324.2</v>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PJ</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
@@ -3809,7 +3529,7 @@
       </c>
       <c r="N22" s="23" t="inlineStr">
         <is>
-          <t>E-mail / Drive corporativo</t>
+          <t>Contabilidade mensal PJ</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3539,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
@@ -3829,12 +3549,12 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PJ</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="F23" s="15" t="inlineStr">
@@ -3844,30 +3564,30 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Custos Escritório</t>
+          <t>Imóvel Feira de Santana</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>Softwares &amp; TI</t>
+          <t>Energia Elétrica (Coelba)</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>OpenAI ChatGPT Subscription</t>
+          <t>Coelba - Energia Casa Feira de Santana (Desalugada)</t>
         </is>
       </c>
       <c r="J23" s="6" t="n">
-        <v>103.13</v>
+        <v>187.45</v>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PJ</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>Normal PJ</t>
+          <t>PJ bancou PF</t>
         </is>
       </c>
       <c r="M23" s="15" t="inlineStr">
@@ -3877,7 +3597,7 @@
       </c>
       <c r="N23" s="23" t="inlineStr">
         <is>
-          <t>Assinatura IA técnica</t>
+          <t>Conta de luz da casa vaga de Feira de Santana paga via PJ</t>
         </is>
       </c>
     </row>
@@ -3887,7 +3607,7 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
@@ -3897,12 +3617,12 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PJ</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="F24" s="15" t="inlineStr">
@@ -3912,30 +3632,30 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Custos Escritório</t>
+          <t>Imóvel Feira de Santana</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Tributos &amp; Taxas</t>
+          <t>Condomínio &amp; Água</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>IOF Compra Internacional (OpenAI)</t>
+          <t>Condomínio Casa Feira de Santana c/ Água (Pjbank)</t>
         </is>
       </c>
       <c r="J24" s="6" t="n">
-        <v>3.6</v>
+        <v>339.34</v>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PJ</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>Normal PJ</t>
+          <t>PJ bancou PF</t>
         </is>
       </c>
       <c r="M24" s="15" t="inlineStr">
@@ -3945,7 +3665,7 @@
       </c>
       <c r="N24" s="23" t="inlineStr">
         <is>
-          <t>IOF cartão corporativo</t>
+          <t>Taxa condominial com água da casa vaga de Feira paga via PJ</t>
         </is>
       </c>
     </row>
@@ -3955,7 +3675,7 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
@@ -3965,7 +3685,7 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PJ</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
@@ -3985,20 +3705,20 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>Viagens &amp; Deslocamento</t>
+          <t>Tributos &amp; Taxas</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aéreas - Parcela 3/3</t>
+          <t>CREA - Conselho Regional de Engenharia (Taxa/Anuidade)</t>
         </is>
       </c>
       <c r="J25" s="6" t="n">
-        <v>246.57</v>
+        <v>228.84</v>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PJ</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -4013,7 +3733,7 @@
       </c>
       <c r="N25" s="23" t="inlineStr">
         <is>
-          <t>ÚLTIMA PARCELA 3/3 - ENCERRADA! Alívio em Novembro!</t>
+          <t>Taxa do conselho regional de engenharia</t>
         </is>
       </c>
     </row>
@@ -4023,7 +3743,7 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
@@ -4033,7 +3753,7 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PJ</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="E26" s="15" t="inlineStr">
@@ -4053,20 +3773,20 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>Operação &amp; Frota</t>
+          <t>Capacitação &amp; Cursos</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Azul Seguros Veicular - Parcela 10/10</t>
+          <t>IPOG - Pós-Graduação Técnica Engenharia</t>
         </is>
       </c>
       <c r="J26" s="6" t="n">
-        <v>238.77</v>
+        <v>309.14</v>
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PJ</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
@@ -4081,7 +3801,7 @@
       </c>
       <c r="N26" s="23" t="inlineStr">
         <is>
-          <t>ÚLTIMA PARCELA 10/10 - ENCERRADA! Alívio em Novembro!</t>
+          <t>Curso de especialização técnica</t>
         </is>
       </c>
     </row>
@@ -4091,7 +3811,7 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
@@ -4101,7 +3821,7 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
@@ -4116,30 +3836,30 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Alimentação</t>
+          <t>Educação (Benjamim)</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>Supermercados</t>
+          <t>Cursos de Idiomas</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Economart (Atacado - Compra do Mês)</t>
+          <t>Spectrum Line Language Center (Inglês Filho)</t>
         </is>
       </c>
       <c r="J27" s="6" t="n">
-        <v>1379.07</v>
+        <v>240</v>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>Normal PF</t>
+          <t>PJ bancou PF</t>
         </is>
       </c>
       <c r="M27" s="15" t="inlineStr">
@@ -4149,7 +3869,7 @@
       </c>
       <c r="N27" s="23" t="inlineStr">
         <is>
-          <t>Grande compra mensal de mantimentos da casa</t>
+          <t>Curso de inglês do filho pago na conta PJ</t>
         </is>
       </c>
     </row>
@@ -4159,7 +3879,7 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
@@ -4169,7 +3889,7 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr">
@@ -4184,30 +3904,30 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Transporte &amp; Veículos</t>
+          <t>Saúde &amp; Bem-Estar</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>Passagens Aéreas</t>
+          <t>Plano de Saúde</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Latam Linhas Aéreas - Parcela 4/4</t>
+          <t>Unimed Pouso Alegre (Plano Família - Boleto 1/3)</t>
         </is>
       </c>
       <c r="J28" s="6" t="n">
-        <v>426.53</v>
+        <v>864.23</v>
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>Normal PF</t>
+          <t>PJ bancou PF</t>
         </is>
       </c>
       <c r="M28" s="15" t="inlineStr">
@@ -4217,7 +3937,7 @@
       </c>
       <c r="N28" s="23" t="inlineStr">
         <is>
-          <t>ÚLTIMA PARCELA 4/4 - ENCERRADA! Alívio em Novembro!</t>
+          <t>Plano de saúde família liquidado via conta PJ</t>
         </is>
       </c>
     </row>
@@ -4227,7 +3947,7 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
@@ -4237,7 +3957,7 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
@@ -4257,25 +3977,25 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>Atividades Físicas</t>
+          <t>Plano de Saúde</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Respect 4 Jiu-Jitsu - Parcela 3/3</t>
+          <t>Unimed Pouso Alegre (Plano Família - Boleto 2/3)</t>
         </is>
       </c>
       <c r="J29" s="6" t="n">
-        <v>165</v>
+        <v>470.79</v>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>Normal PF</t>
+          <t>PJ bancou PF</t>
         </is>
       </c>
       <c r="M29" s="15" t="inlineStr">
@@ -4285,7 +4005,7 @@
       </c>
       <c r="N29" s="23" t="inlineStr">
         <is>
-          <t>ÚLTIMA PARCELA 3/3 - ENCERRADA! Alívio em Novembro!</t>
+          <t>Plano de saúde família liquidado via conta PJ</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4015,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
@@ -4305,7 +4025,7 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
@@ -4320,30 +4040,30 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Compras &amp; Lazer</t>
+          <t>Saúde &amp; Bem-Estar</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>Parcelamentos Antigos</t>
+          <t>Plano de Saúde</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Pg *Pza Comercio - Parcela 4/6</t>
+          <t>Unimed Pouso Alegre (Plano Família - Boleto 3/3)</t>
         </is>
       </c>
       <c r="J30" s="6" t="n">
-        <v>111.63</v>
+        <v>356.83</v>
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Conta Caixa PJ</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>Normal PF</t>
+          <t>PJ bancou PF</t>
         </is>
       </c>
       <c r="M30" s="15" t="inlineStr">
@@ -4353,7 +4073,7 @@
       </c>
       <c r="N30" s="23" t="inlineStr">
         <is>
-          <t>Parcela 4 de 6</t>
+          <t>Plano de saúde família liquidado via conta PJ</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4083,7 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
@@ -4373,7 +4093,7 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Conta Nubank PJ</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
@@ -4388,30 +4108,30 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Saúde &amp; Bem-Estar</t>
+          <t>Educação (Benjamim)</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>Farmácia</t>
+          <t>Escola</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Raia Drogasil - Parcela 1/3</t>
+          <t>Associação Obras Pavonianas de Assis (Colégio Benjamim)</t>
         </is>
       </c>
       <c r="J31" s="6" t="n">
-        <v>112.91</v>
+        <v>1870</v>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Conta Nubank PJ</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>Normal PF</t>
+          <t>PJ bancou PF</t>
         </is>
       </c>
       <c r="M31" s="15" t="inlineStr">
@@ -4421,7 +4141,7 @@
       </c>
       <c r="N31" s="23" t="inlineStr">
         <is>
-          <t>Medicamentos (Parcela 1 de 3)</t>
+          <t>Mensalidade escolar do filho paga via conta Nubank PJ</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4151,7 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
@@ -4441,7 +4161,7 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Conta Caixa PF</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
@@ -4456,25 +4176,25 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Compras &amp; Lazer</t>
+          <t>Alimentação</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>Vestuário / Casa</t>
+          <t>Supermercados</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>Novaalianca</t>
+          <t>Mercadinho 24h (Pix QR)</t>
         </is>
       </c>
       <c r="J32" s="6" t="n">
-        <v>100</v>
+        <v>45.96</v>
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Conta Caixa PF</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
@@ -4489,7 +4209,7 @@
       </c>
       <c r="N32" s="23" t="inlineStr">
         <is>
-          <t>Compras pessoais</t>
+          <t>Mercado reposição</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4219,7 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
@@ -4509,7 +4229,7 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Conta Caixa PF</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
@@ -4529,20 +4249,20 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>Lanches &amp; Sobremesas</t>
+          <t>Feira / Padaria</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Acai do Brunao Ribeira</t>
+          <t>Jose Messias Da Rosa (Feira Pix)</t>
         </is>
       </c>
       <c r="J33" s="6" t="n">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Conta Caixa PF</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -4557,7 +4277,7 @@
       </c>
       <c r="N33" s="23" t="inlineStr">
         <is>
-          <t>Lanches</t>
+          <t>Feira hortifrúti</t>
         </is>
       </c>
     </row>
@@ -4567,7 +4287,7 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
@@ -4577,7 +4297,7 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Conta Caixa PF</t>
         </is>
       </c>
       <c r="E34" s="15" t="inlineStr">
@@ -4592,25 +4312,25 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Moradia (Pouso Alegre)</t>
+          <t>Custos Pessoais</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>Conectividade / Telefone</t>
+          <t>Transferências / Pagamentos PF</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Tim *75992503292</t>
+          <t>Transferência Pix PF Enviada (Chave)</t>
         </is>
       </c>
       <c r="J34" s="6" t="n">
-        <v>60.35</v>
+        <v>500</v>
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Conta Caixa PF</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
@@ -4625,7 +4345,7 @@
       </c>
       <c r="N34" s="23" t="inlineStr">
         <is>
-          <t>Telefonia celular</t>
+          <t>Despesa / transferência pessoal PF</t>
         </is>
       </c>
     </row>
@@ -4635,7 +4355,7 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C35" s="15" t="inlineStr">
@@ -4645,7 +4365,7 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Conta Caixa PF</t>
         </is>
       </c>
       <c r="E35" s="15" t="inlineStr">
@@ -4660,25 +4380,25 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Alimentação</t>
+          <t>Custos Pessoais</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>Restaurantes &amp; Lanches</t>
+          <t>Transferências / Pagamentos PF</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Mariajandirade</t>
+          <t>Transferência Pix PF Enviada (Chave)</t>
         </is>
       </c>
       <c r="J35" s="6" t="n">
-        <v>55.5</v>
+        <v>100</v>
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Conta Caixa PF</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -4693,7 +4413,7 @@
       </c>
       <c r="N35" s="23" t="inlineStr">
         <is>
-          <t>Alimentação</t>
+          <t>Despesa / transferência pessoal PF</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4423,7 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
@@ -4713,7 +4433,7 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Conta Caixa PF</t>
         </is>
       </c>
       <c r="E36" s="15" t="inlineStr">
@@ -4733,20 +4453,20 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>Restaurantes &amp; Lanches</t>
+          <t>Padaria / Lanches</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Pastelaria do Tila</t>
+          <t>E PIX QRD Caixa PF</t>
         </is>
       </c>
       <c r="J36" s="6" t="n">
-        <v>43.5</v>
+        <v>4</v>
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Conta Caixa PF</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
@@ -4761,7 +4481,7 @@
       </c>
       <c r="N36" s="23" t="inlineStr">
         <is>
-          <t>Lanches</t>
+          <t>Lanches / Padaria</t>
         </is>
       </c>
     </row>
@@ -4771,7 +4491,7 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="C37" s="15" t="inlineStr">
@@ -4781,7 +4501,7 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Conta Caixa PF</t>
         </is>
       </c>
       <c r="E37" s="15" t="inlineStr">
@@ -4801,20 +4521,20 @@
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>Supermercados</t>
+          <t>Padaria / Lanches</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Rodrigues Rodrigues Su</t>
+          <t>ENV PIX QE Caixa PF</t>
         </is>
       </c>
       <c r="J37" s="6" t="n">
-        <v>43.27</v>
+        <v>19</v>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Conta Caixa PF</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -4829,7 +4549,7 @@
       </c>
       <c r="N37" s="23" t="inlineStr">
         <is>
-          <t>Mercado</t>
+          <t>Lanches / Padaria</t>
         </is>
       </c>
     </row>
@@ -4839,7 +4559,7 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
@@ -4849,7 +4569,7 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Conta Caixa PF</t>
         </is>
       </c>
       <c r="E38" s="15" t="inlineStr">
@@ -4869,20 +4589,20 @@
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>Restaurantes &amp; Lanches</t>
+          <t>Lanches &amp; Conveniência</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Mariko</t>
+          <t>E PIX QRD Caixa PF</t>
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>40</v>
+        <v>11.99</v>
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Conta Caixa PF</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
@@ -4897,7 +4617,7 @@
       </c>
       <c r="N38" s="23" t="inlineStr">
         <is>
-          <t>Alimentação</t>
+          <t>Lanches / Conveniência</t>
         </is>
       </c>
     </row>
@@ -4907,7 +4627,7 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C39" s="15" t="inlineStr">
@@ -4917,7 +4637,7 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Cartão Caixa PF</t>
         </is>
       </c>
       <c r="E39" s="15" t="inlineStr">
@@ -4937,20 +4657,20 @@
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>Doces / Confeitaria</t>
+          <t>Supermercados</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Cacau Show</t>
+          <t>Rodrigues Rodrigues Su</t>
         </is>
       </c>
       <c r="J39" s="6" t="n">
-        <v>39.99</v>
+        <v>41.75</v>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Cartão Caixa PF</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -4965,7 +4685,7 @@
       </c>
       <c r="N39" s="23" t="inlineStr">
         <is>
-          <t>Doces / Chocolates</t>
+          <t>Supermercado reposição</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4695,7 @@
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
@@ -4985,7 +4705,7 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Cartão Caixa PF</t>
         </is>
       </c>
       <c r="E40" s="15" t="inlineStr">
@@ -5000,25 +4720,25 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Saúde &amp; Bem-Estar</t>
+          <t>Compras &amp; Lazer</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>Farmácia</t>
+          <t>Tarifas Cartão</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Natusfarma 0030 Mg</t>
+          <t>Anuidade Nacional Titular (03/12)</t>
         </is>
       </c>
       <c r="J40" s="6" t="n">
-        <v>39.99</v>
+        <v>5.25</v>
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Cartão Caixa PF</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
@@ -5033,7 +4753,7 @@
       </c>
       <c r="N40" s="23" t="inlineStr">
         <is>
-          <t>Farmácia</t>
+          <t>Anuidade cartão Elo</t>
         </is>
       </c>
     </row>
@@ -5043,7 +4763,7 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C41" s="15" t="inlineStr">
@@ -5053,12 +4773,12 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Cartão Nubank PJ</t>
         </is>
       </c>
       <c r="E41" s="15" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="F41" s="15" t="inlineStr">
@@ -5068,30 +4788,30 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Saúde &amp; Bem-Estar</t>
+          <t>Custos Escritório</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>Farmácia</t>
+          <t>Viagens &amp; Deslocamento</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>Masterformula</t>
+          <t>Gol Linhas Aéreas - Parcela 3/3</t>
         </is>
       </c>
       <c r="J41" s="6" t="n">
-        <v>35.66</v>
+        <v>246.57</v>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Cartão Nubank PJ</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>Normal PF</t>
+          <t>Normal PJ</t>
         </is>
       </c>
       <c r="M41" s="15" t="inlineStr">
@@ -5101,7 +4821,7 @@
       </c>
       <c r="N41" s="23" t="inlineStr">
         <is>
-          <t>Manipulação / Farmácia</t>
+          <t>ÚLTIMA PARCELA 3/3 - ENCERRADA! Alívio em Novembro!</t>
         </is>
       </c>
     </row>
@@ -5111,7 +4831,7 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
@@ -5121,12 +4841,12 @@
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Cartão Nubank PJ</t>
         </is>
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="F42" s="15" t="inlineStr">
@@ -5136,30 +4856,30 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Compras &amp; Lazer</t>
+          <t>Custos Escritório</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>Streaming / TV</t>
+          <t>Operação &amp; Frota</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>Paramount+</t>
+          <t>Azul Seguros Veicular - Parcela 10/10</t>
         </is>
       </c>
       <c r="J42" s="6" t="n">
-        <v>34.9</v>
+        <v>238.77</v>
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Cartão Nubank PJ</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>Normal PF</t>
+          <t>Normal PJ</t>
         </is>
       </c>
       <c r="M42" s="15" t="inlineStr">
@@ -5169,7 +4889,7 @@
       </c>
       <c r="N42" s="23" t="inlineStr">
         <is>
-          <t>Assinatura streaming</t>
+          <t>ÚLTIMA PARCELA 10/10 - ENCERRADA! Alívio em Novembro!</t>
         </is>
       </c>
     </row>
@@ -5179,7 +4899,7 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C43" s="15" t="inlineStr">
@@ -5189,12 +4909,12 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Cartão Nubank PJ</t>
         </is>
       </c>
       <c r="E43" s="15" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="F43" s="15" t="inlineStr">
@@ -5204,30 +4924,30 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Alimentação</t>
+          <t>Custos Escritório</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>Supermercados</t>
+          <t>Softwares &amp; TI</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Supermercado Buritis</t>
+          <t>OpenAI ChatGPT Subscription</t>
         </is>
       </c>
       <c r="J43" s="6" t="n">
-        <v>31.45</v>
+        <v>103.13</v>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Cartão Nubank PJ</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>Normal PF</t>
+          <t>Normal PJ</t>
         </is>
       </c>
       <c r="M43" s="15" t="inlineStr">
@@ -5237,7 +4957,7 @@
       </c>
       <c r="N43" s="23" t="inlineStr">
         <is>
-          <t>Mercado reposição</t>
+          <t>Assinatura IA técnica</t>
         </is>
       </c>
     </row>
@@ -5257,12 +4977,12 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Cartão Nubank PJ</t>
         </is>
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="F44" s="15" t="inlineStr">
@@ -5272,30 +4992,30 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>Alimentação</t>
+          <t>Custos Escritório</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>Supermercados</t>
+          <t>Tributos &amp; Taxas</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Supermercado Buritis</t>
+          <t>IOF Compra Internacional (OpenAI)</t>
         </is>
       </c>
       <c r="J44" s="6" t="n">
-        <v>25.86</v>
+        <v>3.6</v>
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Cartão Nubank PJ</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>Normal PF</t>
+          <t>Normal PJ</t>
         </is>
       </c>
       <c r="M44" s="15" t="inlineStr">
@@ -5305,7 +5025,7 @@
       </c>
       <c r="N44" s="23" t="inlineStr">
         <is>
-          <t>Mercado reposição</t>
+          <t>IOF corporativo</t>
         </is>
       </c>
     </row>
@@ -5315,7 +5035,7 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C45" s="15" t="inlineStr">
@@ -5325,12 +5045,12 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Cartão Nubank PJ</t>
         </is>
       </c>
       <c r="E45" s="15" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="F45" s="15" t="inlineStr">
@@ -5340,30 +5060,30 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Alimentação</t>
+          <t>Custos Escritório</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>Lanches &amp; Sobremesas</t>
+          <t>Softwares &amp; TI</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Chiquinho Sorvetes</t>
+          <t>Google Workspace</t>
         </is>
       </c>
       <c r="J45" s="6" t="n">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Cartão Nubank PJ</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>Normal PF</t>
+          <t>Normal PJ</t>
         </is>
       </c>
       <c r="M45" s="15" t="inlineStr">
@@ -5373,7 +5093,7 @@
       </c>
       <c r="N45" s="23" t="inlineStr">
         <is>
-          <t>Sobremesa</t>
+          <t>E-mail / Drive corporativo</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5103,7 @@
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
@@ -5393,12 +5113,12 @@
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Cartão Nubank PJ</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="F46" s="15" t="inlineStr">
@@ -5408,30 +5128,30 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Compras &amp; Lazer</t>
+          <t>Custos Escritório</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>Streaming / TV</t>
+          <t>Viagens &amp; Deslocamento</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Amazon Prime Canais</t>
+          <t>Latam Linhas Aéreas (Passagem Trabalho)</t>
         </is>
       </c>
       <c r="J46" s="6" t="n">
-        <v>19.99</v>
+        <v>642.49</v>
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Cartão Nubank PJ</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>Normal PF</t>
+          <t>Normal PJ</t>
         </is>
       </c>
       <c r="M46" s="15" t="inlineStr">
@@ -5441,7 +5161,7 @@
       </c>
       <c r="N46" s="23" t="inlineStr">
         <is>
-          <t>Assinatura canais</t>
+          <t>Deslocamento técnico projeto</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5171,7 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="C47" s="15" t="inlineStr">
@@ -5461,12 +5181,12 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Cartão Nubank PJ</t>
         </is>
       </c>
       <c r="E47" s="15" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="F47" s="15" t="inlineStr">
@@ -5476,30 +5196,30 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Alimentação</t>
+          <t>Custos Escritório</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>Supermercados</t>
+          <t>Softwares &amp; TI</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Supermercado Buritis</t>
+          <t>Anthropic Claude Subscription</t>
         </is>
       </c>
       <c r="J47" s="6" t="n">
-        <v>18.19</v>
+        <v>113.95</v>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Cartão Nubank PJ</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>Normal PF</t>
+          <t>Normal PJ</t>
         </is>
       </c>
       <c r="M47" s="15" t="inlineStr">
@@ -5509,7 +5229,7 @@
       </c>
       <c r="N47" s="23" t="inlineStr">
         <is>
-          <t>Mercado reposição</t>
+          <t>Assinatura IA técnica Claude</t>
         </is>
       </c>
     </row>
@@ -5519,7 +5239,7 @@
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="C48" s="15" t="inlineStr">
@@ -5529,12 +5249,12 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Cartão Nubank PJ</t>
         </is>
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="F48" s="15" t="inlineStr">
@@ -5544,30 +5264,30 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Alimentação</t>
+          <t>Custos Escritório</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>Padaria / Lanches</t>
+          <t>Tributos &amp; Taxas</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Mp *Rosinairibeir</t>
+          <t>IOF Compra Internacional (Anthropic)</t>
         </is>
       </c>
       <c r="J48" s="6" t="n">
-        <v>18</v>
+        <v>3.98</v>
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Cartão Nubank PJ</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>Normal PF</t>
+          <t>Normal PJ</t>
         </is>
       </c>
       <c r="M48" s="15" t="inlineStr">
@@ -5577,7 +5297,7 @@
       </c>
       <c r="N48" s="23" t="inlineStr">
         <is>
-          <t>Padaria</t>
+          <t>IOF corporativo</t>
         </is>
       </c>
     </row>
@@ -5587,7 +5307,7 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="C49" s="15" t="inlineStr">
@@ -5597,12 +5317,12 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Cartão Nubank PJ</t>
         </is>
       </c>
       <c r="E49" s="15" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="F49" s="15" t="inlineStr">
@@ -5612,30 +5332,30 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Alimentação</t>
+          <t>Custos Escritório</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>Padaria / Lanches</t>
+          <t>Softwares &amp; TI</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>Mp *Rosinairibeir</t>
+          <t>Anthropic Claude Sub / API</t>
         </is>
       </c>
       <c r="J49" s="6" t="n">
-        <v>14.5</v>
+        <v>467.87</v>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Cartão Nubank PJ</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>Normal PF</t>
+          <t>Normal PJ</t>
         </is>
       </c>
       <c r="M49" s="15" t="inlineStr">
@@ -5645,7 +5365,7 @@
       </c>
       <c r="N49" s="23" t="inlineStr">
         <is>
-          <t>Padaria</t>
+          <t>Assinatura / Créditos IA Claude</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5375,7 @@
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="C50" s="15" t="inlineStr">
@@ -5665,12 +5385,12 @@
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Cartão Nubank PJ</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="F50" s="15" t="inlineStr">
@@ -5680,30 +5400,30 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Alimentação</t>
+          <t>Custos Escritório</t>
         </is>
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>Padaria / Lanches</t>
+          <t>Tributos &amp; Taxas</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Casa da Coxinha</t>
+          <t>IOF Compra Internacional (Anthropic)</t>
         </is>
       </c>
       <c r="J50" s="6" t="n">
-        <v>14</v>
+        <v>16.37</v>
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>Cartão Nubank PF</t>
+          <t>Cartão Nubank PJ</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>Normal PF</t>
+          <t>Normal PJ</t>
         </is>
       </c>
       <c r="M50" s="15" t="inlineStr">
@@ -5713,7 +5433,7 @@
       </c>
       <c r="N50" s="23" t="inlineStr">
         <is>
-          <t>Lanches</t>
+          <t>IOF corporativo</t>
         </is>
       </c>
     </row>
@@ -5723,7 +5443,7 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C51" s="15" t="inlineStr">
@@ -5748,21 +5468,21 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Alimentação</t>
+          <t>Transporte &amp; Veículos</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>Padaria / Lanches</t>
+          <t>Passagens Aéreas</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Casa da Coxinha</t>
+          <t>Latam Linhas Aéreas - Parcela 4/4</t>
         </is>
       </c>
       <c r="J51" s="6" t="n">
-        <v>13.5</v>
+        <v>426.53</v>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
@@ -5781,7 +5501,7 @@
       </c>
       <c r="N51" s="23" t="inlineStr">
         <is>
-          <t>Lanches</t>
+          <t>ÚLTIMA PARCELA 4/4 - ENCERRADA! Alívio em Novembro!</t>
         </is>
       </c>
     </row>
@@ -5816,21 +5536,21 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Educação (Benjamim)</t>
+          <t>Saúde &amp; Bem-Estar</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>Material Escolar</t>
+          <t>Atividades Físicas</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Papelaria Lapis de Cor</t>
+          <t>Respect 4 Jiu-Jitsu - Parcela 3/3</t>
         </is>
       </c>
       <c r="J52" s="6" t="n">
-        <v>9.5</v>
+        <v>165</v>
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
@@ -5849,7 +5569,7 @@
       </c>
       <c r="N52" s="23" t="inlineStr">
         <is>
-          <t>Papelaria</t>
+          <t>ÚLTIMA PARCELA 3/3 - ENCERRADA! Alívio em Novembro!</t>
         </is>
       </c>
     </row>
@@ -5859,70 +5579,4354 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E53" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F53" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>Compras &amp; Lazer</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>Parcelamentos Antigos</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>Pg *Pza Comercio - Parcela 4/6</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="n">
+        <v>111.63</v>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M53" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N53" s="23" t="inlineStr">
+        <is>
+          <t>Parcela 4 de 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="15" t="n">
+        <v>1053</v>
+      </c>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E54" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F54" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>Compras &amp; Lazer</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>Vestuário / Casa</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>Novaalianca</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="K54" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M54" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N54" s="23" t="inlineStr">
+        <is>
+          <t>Compras pessoais</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="15" t="n">
+        <v>1054</v>
+      </c>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E55" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F55" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>Padaria / Lanches</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>Mp *Rosinairibeir</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M55" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N55" s="23" t="inlineStr">
+        <is>
+          <t>Padaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="n">
+        <v>1055</v>
+      </c>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E56" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F56" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>Educação (Benjamim)</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>Material Escolar</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>Papelaria Lapis de Cor</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K56" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M56" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N56" s="23" t="inlineStr">
+        <is>
+          <t>Papelaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="15" t="n">
+        <v>1056</v>
+      </c>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C57" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E57" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F57" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>Supermercados</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>Supermercado Buritis</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M57" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N57" s="23" t="inlineStr">
+        <is>
+          <t>Mercado reposição</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="n">
+        <v>1057</v>
+      </c>
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C58" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E58" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F58" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>Compras &amp; Lazer</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>Streaming / TV</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>Amazon Prime Canais</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="K58" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M58" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N58" s="23" t="inlineStr">
+        <is>
+          <t>Assinatura canais</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="n">
+        <v>1058</v>
+      </c>
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C59" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E59" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F59" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>Padaria / Lanches</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>Mp *Rosinairibeir</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M59" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N59" s="23" t="inlineStr">
+        <is>
+          <t>Padaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="15" t="n">
+        <v>1059</v>
+      </c>
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C60" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E60" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F60" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>Saúde &amp; Bem-Estar</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>Farmácia</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>Natusfarma 0030 Mg</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="n">
+        <v>39.99</v>
+      </c>
+      <c r="K60" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M60" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N60" s="23" t="inlineStr">
+        <is>
+          <t>Farmácia</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="15" t="n">
+        <v>1060</v>
+      </c>
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C61" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E61" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F61" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Compras &amp; Lazer</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>Streaming / TV</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>Paramount+</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M61" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N61" s="23" t="inlineStr">
+        <is>
+          <t>Assinatura streaming</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="15" t="n">
+        <v>1061</v>
+      </c>
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C62" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E62" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F62" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>Supermercados</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>Supermercado Buritis</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="K62" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M62" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N62" s="23" t="inlineStr">
+        <is>
+          <t>Mercado reposição</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="15" t="n">
+        <v>1062</v>
+      </c>
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C63" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E63" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F63" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>Supermercados</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>Supermercado Buritis</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M63" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N63" s="23" t="inlineStr">
+        <is>
+          <t>Mercado reposição</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="15" t="n">
+        <v>1063</v>
+      </c>
+      <c r="B64" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C64" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E64" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F64" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>Padaria / Lanches</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>Casa da Coxinha</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="K64" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M64" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N64" s="23" t="inlineStr">
+        <is>
+          <t>Lanches</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="15" t="n">
+        <v>1064</v>
+      </c>
+      <c r="B65" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C65" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E65" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F65" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>Supermercados</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>Economart (Atacado - Compra do Mês)</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="n">
+        <v>1379.07</v>
+      </c>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M65" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N65" s="23" t="inlineStr">
+        <is>
+          <t>Grande compra mensal de mantimentos da casa</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="15" t="n">
+        <v>1065</v>
+      </c>
+      <c r="B66" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C66" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E66" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F66" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>Saúde &amp; Bem-Estar</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>Farmácia</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>Raia Drogasil - Parcela 1/3</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="n">
+        <v>112.91</v>
+      </c>
+      <c r="K66" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M66" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N66" s="23" t="inlineStr">
+        <is>
+          <t>Medicamentos (Parcela 1 de 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="15" t="n">
+        <v>1066</v>
+      </c>
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C67" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E67" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F67" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>Restaurantes &amp; Lanches</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>Pastelaria do Tila</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M67" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N67" s="23" t="inlineStr">
+        <is>
+          <t>Lanches</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="15" t="n">
+        <v>1067</v>
+      </c>
+      <c r="B68" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C68" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E68" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F68" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>Doces / Confeitaria</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>Cacau Show</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="n">
+        <v>39.99</v>
+      </c>
+      <c r="K68" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M68" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N68" s="23" t="inlineStr">
+        <is>
+          <t>Doces / Chocolates</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="15" t="n">
+        <v>1068</v>
+      </c>
+      <c r="B69" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C69" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E69" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F69" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>Lanches &amp; Sobremesas</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>Chiquinho Sorvetes</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M69" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N69" s="23" t="inlineStr">
+        <is>
+          <t>Sobremesa</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="15" t="n">
+        <v>1069</v>
+      </c>
+      <c r="B70" s="15" t="inlineStr">
+        <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="C53" s="15" t="inlineStr">
+      <c r="C70" s="15" t="inlineStr">
         <is>
           <t>10/2026</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>Cartão Nubank PF</t>
-        </is>
-      </c>
-      <c r="E53" s="15" t="inlineStr">
-        <is>
-          <t>PF</t>
-        </is>
-      </c>
-      <c r="F53" s="15" t="inlineStr">
-        <is>
-          <t>Despesa</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E70" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F70" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
         <is>
           <t>Alimentação</t>
         </is>
       </c>
-      <c r="H53" s="7" t="inlineStr">
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>Lanches &amp; Sobremesas</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>Acai do Brunao Ribeira</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="K70" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M70" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N70" s="23" t="inlineStr">
+        <is>
+          <t>Lanches</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="15" t="n">
+        <v>1070</v>
+      </c>
+      <c r="B71" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C71" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E71" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F71" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
         <is>
           <t>Restaurantes &amp; Lanches</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>Mariajandirade</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M71" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N71" s="23" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="15" t="n">
+        <v>1071</v>
+      </c>
+      <c r="B72" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C72" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E72" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F72" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>Restaurantes &amp; Lanches</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>Mariko</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="K72" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M72" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N72" s="23" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="15" t="n">
+        <v>1072</v>
+      </c>
+      <c r="B73" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C73" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E73" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F73" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>Restaurantes &amp; Lanches</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
         <is>
           <t>Porto Bello Restaurant</t>
         </is>
       </c>
-      <c r="J53" s="6" t="n">
+      <c r="J73" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="K53" s="7" t="inlineStr">
-        <is>
-          <t>Cartão Nubank PF</t>
-        </is>
-      </c>
-      <c r="L53" s="5" t="inlineStr">
+      <c r="K73" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
         <is>
           <t>Normal PF</t>
         </is>
       </c>
-      <c r="M53" s="15" t="inlineStr">
-        <is>
-          <t>Liquidado</t>
-        </is>
-      </c>
-      <c r="N53" s="23" t="inlineStr">
+      <c r="M73" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N73" s="23" t="inlineStr">
         <is>
           <t>Lanches</t>
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="15" t="n">
+        <v>1073</v>
+      </c>
+      <c r="B74" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C74" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E74" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F74" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>Padaria / Lanches</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>Casa da Coxinha</t>
+        </is>
+      </c>
+      <c r="J74" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="K74" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L74" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M74" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N74" s="23" t="inlineStr">
+        <is>
+          <t>Lanches</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="15" t="n">
+        <v>1074</v>
+      </c>
+      <c r="B75" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C75" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E75" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F75" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>Moradia (Pouso Alegre)</t>
+        </is>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>Conectividade / Telefone</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>Tim *75992503292</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="n">
+        <v>60.35</v>
+      </c>
+      <c r="K75" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M75" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N75" s="23" t="inlineStr">
+        <is>
+          <t>Telefonia celular pessoal</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="15" t="n">
+        <v>1075</v>
+      </c>
+      <c r="B76" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C76" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E76" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F76" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>Supermercados</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>Rodrigues Rodrigues Su</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="n">
+        <v>43.27</v>
+      </c>
+      <c r="K76" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L76" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M76" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N76" s="23" t="inlineStr">
+        <is>
+          <t>Supermercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="15" t="n">
+        <v>1076</v>
+      </c>
+      <c r="B77" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C77" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E77" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F77" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Saúde &amp; Bem-Estar</t>
+        </is>
+      </c>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>Farmácia</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>Masterformula</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="n">
+        <v>35.66</v>
+      </c>
+      <c r="K77" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M77" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N77" s="23" t="inlineStr">
+        <is>
+          <t>Farmácia manipulação</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="15" t="n">
+        <v>1077</v>
+      </c>
+      <c r="B78" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E78" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F78" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>Compras &amp; Lazer</t>
+        </is>
+      </c>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>Estornos</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>Estorno de compra (Amazon Prime)</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="n">
+        <v>-19.99</v>
+      </c>
+      <c r="K78" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M78" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N78" s="23" t="inlineStr">
+        <is>
+          <t>Estorno de assinatura Amazon Prime duplicada</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="15" t="n">
+        <v>1078</v>
+      </c>
+      <c r="B79" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C79" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E79" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F79" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>Compras &amp; Lazer</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>Estornos</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>Estorno de compra (Amazon Prime)</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="n">
+        <v>-44.9</v>
+      </c>
+      <c r="K79" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M79" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N79" s="23" t="inlineStr">
+        <is>
+          <t>Estorno de compra Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="15" t="n">
+        <v>1079</v>
+      </c>
+      <c r="B80" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E80" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F80" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>Compras &amp; Lazer</t>
+        </is>
+      </c>
+      <c r="H80" s="7" t="inlineStr">
+        <is>
+          <t>Casa &amp; Utilidades</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>Mercadolivre (Compras Casa/Utilidades)</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="n">
+        <v>435.53</v>
+      </c>
+      <c r="K80" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L80" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M80" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N80" s="23" t="inlineStr">
+        <is>
+          <t>Compra de utilidades no Mercado Livre</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="15" t="n">
+        <v>1080</v>
+      </c>
+      <c r="B81" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C81" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E81" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F81" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>Supermercados</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>Supermercado Buritis</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="n">
+        <v>111.94</v>
+      </c>
+      <c r="K81" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M81" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N81" s="23" t="inlineStr">
+        <is>
+          <t>Supermercado reposição</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="15" t="n">
+        <v>1081</v>
+      </c>
+      <c r="B82" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C82" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E82" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F82" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>Transporte &amp; Veículos</t>
+        </is>
+      </c>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>Combustível</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>Postosilviano (Combustível)</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="K82" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L82" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M82" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N82" s="23" t="inlineStr">
+        <is>
+          <t>Abastecimento veículo</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="15" t="n">
+        <v>1082</v>
+      </c>
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C83" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E83" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F83" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>Compras &amp; Lazer</t>
+        </is>
+      </c>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>Casa &amp; Utilidades</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>Lojas Prado</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="K83" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L83" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M83" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N83" s="23" t="inlineStr">
+        <is>
+          <t>Utilidades</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="15" t="n">
+        <v>1083</v>
+      </c>
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C84" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E84" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F84" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>Lanches &amp; Confeitaria</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>Jim.Com* Feito em Casa</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="K84" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L84" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M84" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N84" s="23" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="15" t="n">
+        <v>1084</v>
+      </c>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="C85" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E85" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F85" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>Saúde &amp; Bem-Estar</t>
+        </is>
+      </c>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>Atividades Físicas</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>Alliance Pouso Alegre (Jiu-Jitsu)</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="K85" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L85" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M85" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N85" s="23" t="inlineStr">
+        <is>
+          <t>Mensalidade Jiu-Jitsu Alliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="15" t="n">
+        <v>1085</v>
+      </c>
+      <c r="B86" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="C86" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E86" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F86" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H86" s="7" t="inlineStr">
+        <is>
+          <t>Restaurantes &amp; Lazer</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>Salvadortoledo</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="n">
+        <v>222</v>
+      </c>
+      <c r="K86" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L86" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M86" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N86" s="23" t="inlineStr">
+        <is>
+          <t>Alimentação / Restaurante</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="15" t="n">
+        <v>1086</v>
+      </c>
+      <c r="B87" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="C87" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E87" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F87" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>Compras &amp; Lazer</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>Eletrônicos &amp; Casa</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>Amazon Br *Amazon</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="n">
+        <v>199.99</v>
+      </c>
+      <c r="K87" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L87" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M87" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N87" s="23" t="inlineStr">
+        <is>
+          <t>Compras Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="15" t="n">
+        <v>1087</v>
+      </c>
+      <c r="B88" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="C88" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E88" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F88" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>Compras &amp; Lazer</t>
+        </is>
+      </c>
+      <c r="H88" s="7" t="inlineStr">
+        <is>
+          <t>Livros &amp; Casa</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>Amazonmktplc*Amazon</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="n">
+        <v>140.17</v>
+      </c>
+      <c r="K88" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L88" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M88" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N88" s="23" t="inlineStr">
+        <is>
+          <t>Compras Amazon Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="15" t="n">
+        <v>1088</v>
+      </c>
+      <c r="B89" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="C89" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E89" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F89" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>Casa &amp; Pet</t>
+        </is>
+      </c>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>Petshop &amp; Agropecuária</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>Petagro</t>
+        </is>
+      </c>
+      <c r="J89" s="6" t="n">
+        <v>134</v>
+      </c>
+      <c r="K89" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L89" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M89" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N89" s="23" t="inlineStr">
+        <is>
+          <t>Petshop / Rações</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="15" t="n">
+        <v>1089</v>
+      </c>
+      <c r="B90" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="C90" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E90" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F90" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>Compras &amp; Lazer</t>
+        </is>
+      </c>
+      <c r="H90" s="7" t="inlineStr">
+        <is>
+          <t>Lazer &amp; Parques</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>Parque Capivari</t>
+        </is>
+      </c>
+      <c r="J90" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K90" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L90" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M90" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N90" s="23" t="inlineStr">
+        <is>
+          <t>Passeio em família</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="15" t="n">
+        <v>1090</v>
+      </c>
+      <c r="B91" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="C91" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E91" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F91" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>Restaurantes</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>Fumacinha</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="n">
+        <v>47.35</v>
+      </c>
+      <c r="K91" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L91" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M91" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N91" s="23" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="15" t="n">
+        <v>1091</v>
+      </c>
+      <c r="B92" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="C92" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E92" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F92" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H92" s="7" t="inlineStr">
+        <is>
+          <t>Doces / Confeitaria</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>Cintia Serafim Chocolates</t>
+        </is>
+      </c>
+      <c r="J92" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="K92" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L92" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M92" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N92" s="23" t="inlineStr">
+        <is>
+          <t>Doces / Chocolates</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="15" t="n">
+        <v>1092</v>
+      </c>
+      <c r="B93" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="C93" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E93" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F93" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>Doces / Confeitaria</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>Cintia Serafim Chocolates</t>
+        </is>
+      </c>
+      <c r="J93" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="K93" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L93" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M93" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N93" s="23" t="inlineStr">
+        <is>
+          <t>Doces / Chocolates</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="15" t="n">
+        <v>1093</v>
+      </c>
+      <c r="B94" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="C94" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E94" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F94" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>Doces / Confeitaria</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>Cintia Serafim Chocolates</t>
+        </is>
+      </c>
+      <c r="J94" s="6" t="n">
+        <v>25.83</v>
+      </c>
+      <c r="K94" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L94" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M94" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N94" s="23" t="inlineStr">
+        <is>
+          <t>Doces / Chocolates</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="15" t="n">
+        <v>1094</v>
+      </c>
+      <c r="B95" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C95" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E95" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F95" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>Transporte &amp; Veículos</t>
+        </is>
+      </c>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>Combustível</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="inlineStr">
+        <is>
+          <t>Auto Posto e Restaurante</t>
+        </is>
+      </c>
+      <c r="J95" s="6" t="n">
+        <v>99.02</v>
+      </c>
+      <c r="K95" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L95" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M95" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N95" s="23" t="inlineStr">
+        <is>
+          <t>Combustível</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="15" t="n">
+        <v>1095</v>
+      </c>
+      <c r="B96" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C96" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E96" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F96" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H96" s="7" t="inlineStr">
+        <is>
+          <t>Restaurantes</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>Churrascaria Gramado</t>
+        </is>
+      </c>
+      <c r="J96" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="K96" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L96" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M96" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N96" s="23" t="inlineStr">
+        <is>
+          <t>Almoço família</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="15" t="n">
+        <v>1096</v>
+      </c>
+      <c r="B97" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C97" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E97" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F97" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>Supermercados</t>
+        </is>
+      </c>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>Rodrigues Rodrigues Su</t>
+        </is>
+      </c>
+      <c r="J97" s="6" t="n">
+        <v>86.04000000000001</v>
+      </c>
+      <c r="K97" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L97" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M97" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N97" s="23" t="inlineStr">
+        <is>
+          <t>Supermercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="15" t="n">
+        <v>1097</v>
+      </c>
+      <c r="B98" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C98" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E98" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F98" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>Compras &amp; Lazer</t>
+        </is>
+      </c>
+      <c r="H98" s="7" t="inlineStr">
+        <is>
+          <t>Serviços &amp; Lazer</t>
+        </is>
+      </c>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>Lucasdiegobalsant</t>
+        </is>
+      </c>
+      <c r="J98" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="K98" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L98" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M98" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N98" s="23" t="inlineStr">
+        <is>
+          <t>Serviços / Lazer</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="15" t="n">
+        <v>1098</v>
+      </c>
+      <c r="B99" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C99" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E99" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F99" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>Lanches</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
+          <t>Jessica Alves Rodrigues</t>
+        </is>
+      </c>
+      <c r="J99" s="6" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="K99" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L99" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M99" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N99" s="23" t="inlineStr">
+        <is>
+          <t>Lanches</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="15" t="n">
+        <v>1099</v>
+      </c>
+      <c r="B100" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C100" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E100" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F100" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H100" s="7" t="inlineStr">
+        <is>
+          <t>Lanches</t>
+        </is>
+      </c>
+      <c r="I100" s="5" t="inlineStr">
+        <is>
+          <t>Maria Eduarda (Lanches)</t>
+        </is>
+      </c>
+      <c r="J100" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K100" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L100" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M100" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N100" s="23" t="inlineStr">
+        <is>
+          <t>Lanches</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="15" t="n">
+        <v>1100</v>
+      </c>
+      <c r="B101" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C101" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E101" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F101" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>Transporte &amp; Veículos</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="inlineStr">
+        <is>
+          <t>Pedágios</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>Pedágio P2</t>
+        </is>
+      </c>
+      <c r="J101" s="6" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="K101" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L101" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M101" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N101" s="23" t="inlineStr">
+        <is>
+          <t>Pedágio viagem</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="15" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B102" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C102" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E102" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F102" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>Transporte &amp; Veículos</t>
+        </is>
+      </c>
+      <c r="H102" s="7" t="inlineStr">
+        <is>
+          <t>Pedágios</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>Pedágio P4</t>
+        </is>
+      </c>
+      <c r="J102" s="6" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="K102" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L102" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M102" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N102" s="23" t="inlineStr">
+        <is>
+          <t>Pedágio viagem</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="15" t="n">
+        <v>1102</v>
+      </c>
+      <c r="B103" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C103" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E103" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F103" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H103" s="7" t="inlineStr">
+        <is>
+          <t>Lanches &amp; Conveniência</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>Crb Fpay</t>
+        </is>
+      </c>
+      <c r="J103" s="6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="K103" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L103" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M103" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N103" s="23" t="inlineStr">
+        <is>
+          <t>Lanches</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="15" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B104" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C104" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E104" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F104" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>Transporte &amp; Veículos</t>
+        </is>
+      </c>
+      <c r="H104" s="7" t="inlineStr">
+        <is>
+          <t>Pedágios</t>
+        </is>
+      </c>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>Pedágio P1</t>
+        </is>
+      </c>
+      <c r="J104" s="6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="K104" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L104" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M104" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N104" s="23" t="inlineStr">
+        <is>
+          <t>Pedágio viagem</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="15" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B105" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C105" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E105" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F105" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>Compras &amp; Lazer</t>
+        </is>
+      </c>
+      <c r="H105" s="7" t="inlineStr">
+        <is>
+          <t>Streaming / TV</t>
+        </is>
+      </c>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>Netflix.Com</t>
+        </is>
+      </c>
+      <c r="J105" s="6" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="K105" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L105" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M105" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N105" s="23" t="inlineStr">
+        <is>
+          <t>Assinatura Netflix</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="15" t="n">
+        <v>1105</v>
+      </c>
+      <c r="B106" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C106" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E106" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F106" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>Compras &amp; Lazer</t>
+        </is>
+      </c>
+      <c r="H106" s="7" t="inlineStr">
+        <is>
+          <t>Streaming / Música</t>
+        </is>
+      </c>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>Ebn*Spotify</t>
+        </is>
+      </c>
+      <c r="J106" s="6" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="K106" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L106" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M106" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N106" s="23" t="inlineStr">
+        <is>
+          <t>Assinatura Spotify</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="15" t="n">
+        <v>1106</v>
+      </c>
+      <c r="B107" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C107" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E107" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F107" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>Saúde &amp; Bem-Estar</t>
+        </is>
+      </c>
+      <c r="H107" s="7" t="inlineStr">
+        <is>
+          <t>Farmácia</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>Masterformula</t>
+        </is>
+      </c>
+      <c r="J107" s="6" t="n">
+        <v>99.76000000000001</v>
+      </c>
+      <c r="K107" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L107" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M107" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N107" s="23" t="inlineStr">
+        <is>
+          <t>Manipulação / Farmácia</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="15" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B108" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C108" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E108" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F108" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H108" s="7" t="inlineStr">
+        <is>
+          <t>Supermercados</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>Tambau Supermercados</t>
+        </is>
+      </c>
+      <c r="J108" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="K108" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L108" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M108" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N108" s="23" t="inlineStr">
+        <is>
+          <t>Supermercado reposição</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="15" t="n">
+        <v>1108</v>
+      </c>
+      <c r="B109" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C109" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E109" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F109" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>Compras &amp; Lazer</t>
+        </is>
+      </c>
+      <c r="H109" s="7" t="inlineStr">
+        <is>
+          <t>Casa &amp; Decoração</t>
+        </is>
+      </c>
+      <c r="I109" s="5" t="inlineStr">
+        <is>
+          <t>Cantaro Interiores</t>
+        </is>
+      </c>
+      <c r="J109" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="K109" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L109" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M109" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N109" s="23" t="inlineStr">
+        <is>
+          <t>Casa &amp; Decoração</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="15" t="n">
+        <v>1109</v>
+      </c>
+      <c r="B110" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C110" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E110" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F110" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>Transporte &amp; Veículos</t>
+        </is>
+      </c>
+      <c r="H110" s="7" t="inlineStr">
+        <is>
+          <t>Combustível</t>
+        </is>
+      </c>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>Posto Pedra Forte Ii</t>
+        </is>
+      </c>
+      <c r="J110" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="K110" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L110" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M110" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N110" s="23" t="inlineStr">
+        <is>
+          <t>Combustível</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="15" t="n">
+        <v>1110</v>
+      </c>
+      <c r="B111" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C111" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E111" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F111" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H111" s="7" t="inlineStr">
+        <is>
+          <t>Hortifrúti &amp; Mercado</t>
+        </is>
+      </c>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>Varejao e Supermercado</t>
+        </is>
+      </c>
+      <c r="J111" s="6" t="n">
+        <v>114.6</v>
+      </c>
+      <c r="K111" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L111" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M111" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N111" s="23" t="inlineStr">
+        <is>
+          <t>Hortifrúti e compras semanais</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="15" t="n">
+        <v>1111</v>
+      </c>
+      <c r="B112" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C112" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E112" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F112" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>Compras &amp; Lazer</t>
+        </is>
+      </c>
+      <c r="H112" s="7" t="inlineStr">
+        <is>
+          <t>Casa &amp; Decoração</t>
+        </is>
+      </c>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>Cantaro Interiores</t>
+        </is>
+      </c>
+      <c r="J112" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="K112" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L112" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M112" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N112" s="23" t="inlineStr">
+        <is>
+          <t>Casa &amp; Decoração</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="15" t="n">
+        <v>1112</v>
+      </c>
+      <c r="B113" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C113" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E113" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F113" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H113" s="7" t="inlineStr">
+        <is>
+          <t>Lanches &amp; Conveniência</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>Conven Pedra Forte</t>
+        </is>
+      </c>
+      <c r="J113" s="6" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="K113" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L113" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M113" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N113" s="23" t="inlineStr">
+        <is>
+          <t>Lanches</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="15" t="n">
+        <v>1113</v>
+      </c>
+      <c r="B114" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C114" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E114" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F114" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>Transporte &amp; Veículos</t>
+        </is>
+      </c>
+      <c r="H114" s="7" t="inlineStr">
+        <is>
+          <t>Combustível</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>Auto Posto Santa Giann</t>
+        </is>
+      </c>
+      <c r="J114" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="K114" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L114" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M114" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N114" s="23" t="inlineStr">
+        <is>
+          <t>Combustível</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="15" t="n">
+        <v>1114</v>
+      </c>
+      <c r="B115" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C115" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E115" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F115" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="H115" s="7" t="inlineStr">
+        <is>
+          <t>Doces / Confeitaria</t>
+        </is>
+      </c>
+      <c r="I115" s="5" t="inlineStr">
+        <is>
+          <t>Doces Flormel</t>
+        </is>
+      </c>
+      <c r="J115" s="6" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="K115" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L115" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M115" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N115" s="23" t="inlineStr">
+        <is>
+          <t>Doces saudáveis</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="15" t="n">
+        <v>1115</v>
+      </c>
+      <c r="B116" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C116" s="15" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="E116" s="15" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F116" s="15" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>Transporte &amp; Veículos</t>
+        </is>
+      </c>
+      <c r="H116" s="7" t="inlineStr">
+        <is>
+          <t>Combustível</t>
+        </is>
+      </c>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>Cityposto</t>
+        </is>
+      </c>
+      <c r="J116" s="6" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="K116" s="7" t="inlineStr">
+        <is>
+          <t>Cartão Nubank PF</t>
+        </is>
+      </c>
+      <c r="L116" s="5" t="inlineStr">
+        <is>
+          <t>Normal PF</t>
+        </is>
+      </c>
+      <c r="M116" s="15" t="inlineStr">
+        <is>
+          <t>Liquidado</t>
+        </is>
+      </c>
+      <c r="N116" s="23" t="inlineStr">
+        <is>
+          <t>Combustível</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N53"/>
+  <autoFilter ref="A1:N116"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
